--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260622.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>34,782,298</t>
+          <t>356,151,305</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>356,151,305</t>
+          <t>34,782,298</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>20,293,230</t>
+          <t>16,379,960</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>16,379,960</t>
+          <t>20,293,230</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
